--- a/Externals/Week 10 Practice.xlsx
+++ b/Externals/Week 10 Practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kemenkeu-my.sharepoint.com/personal/teuku_radarma_kemenkeu_go_id/Documents/PKN STAN/Audit SI/Externals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{756B054D-9CD3-4E34-9420-B58C31297E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{756B054D-9CD3-4E34-9420-B58C31297E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DA666BF-CE91-46A6-8172-DA8A3E41CCD9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{BB5D335C-04CC-4BA7-9CA4-853D50C6FB73}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{BB5D335C-04CC-4BA7-9CA4-853D50C6FB73}"/>
   </bookViews>
   <sheets>
     <sheet name="INVENTORY" sheetId="1" r:id="rId1"/>
@@ -633,14 +633,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBFE34E-AF71-4669-A4D5-DFB78BFB7491}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +651,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -661,11 +661,8 @@
       <c r="C2">
         <v>100000</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -675,11 +672,8 @@
       <c r="C3">
         <v>120000</v>
       </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -689,11 +683,8 @@
       <c r="C4">
         <v>60000</v>
       </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -703,11 +694,8 @@
       <c r="C5">
         <v>30000</v>
       </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -717,11 +705,8 @@
       <c r="C6">
         <v>110000</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -731,11 +716,8 @@
       <c r="C7">
         <v>90000</v>
       </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -745,11 +727,8 @@
       <c r="C8">
         <v>100000</v>
       </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -759,11 +738,8 @@
       <c r="C9">
         <v>40000</v>
       </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -773,11 +749,8 @@
       <c r="C10">
         <v>80000</v>
       </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -787,11 +760,8 @@
       <c r="C11">
         <v>150000</v>
       </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -801,11 +771,8 @@
       <c r="C12">
         <v>150000</v>
       </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -815,11 +782,8 @@
       <c r="C13">
         <v>50000</v>
       </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -828,9 +792,6 @@
       </c>
       <c r="C14">
         <v>30000</v>
-      </c>
-      <c r="F14">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -844,13 +805,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA914B64-655B-4669-A069-9DD2BE29342D}">
   <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.9296875" customWidth="1"/>
+    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -867,7 +828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>44197</v>
       </c>
@@ -884,7 +845,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>44200</v>
       </c>
@@ -901,7 +862,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>44203</v>
       </c>
@@ -918,7 +879,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>44205</v>
       </c>
@@ -935,7 +896,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>44206</v>
       </c>
@@ -952,7 +913,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>44209</v>
       </c>
@@ -969,7 +930,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>44211</v>
       </c>
@@ -986,7 +947,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>44214</v>
       </c>
@@ -1003,7 +964,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>44215</v>
       </c>
@@ -1020,7 +981,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>44216</v>
       </c>
@@ -1037,7 +998,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>44220</v>
       </c>
@@ -1054,7 +1015,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>44221</v>
       </c>
@@ -1071,7 +1032,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>44224</v>
       </c>
@@ -1088,7 +1049,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>44227</v>
       </c>
@@ -1105,7 +1066,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>44228</v>
       </c>
@@ -1122,7 +1083,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>44230</v>
       </c>
@@ -1139,7 +1100,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>44231</v>
       </c>
@@ -1156,7 +1117,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>44233</v>
       </c>
@@ -1173,7 +1134,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>44234</v>
       </c>
@@ -1190,7 +1151,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>44238</v>
       </c>
@@ -1207,7 +1168,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>44241</v>
       </c>
@@ -1224,7 +1185,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>44243</v>
       </c>
@@ -1241,7 +1202,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>44244</v>
       </c>
@@ -1258,7 +1219,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>44245</v>
       </c>
@@ -1272,7 +1233,7 @@
         <v>450000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>44249</v>
       </c>
@@ -1289,7 +1250,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>44250</v>
       </c>
@@ -1306,7 +1267,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>44252</v>
       </c>
@@ -1323,7 +1284,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>44256</v>
       </c>
@@ -1340,7 +1301,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>44257</v>
       </c>
@@ -1357,7 +1318,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>44258</v>
       </c>
@@ -1374,7 +1335,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>44262</v>
       </c>
@@ -1391,7 +1352,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>44265</v>
       </c>
@@ -1408,7 +1369,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>44266</v>
       </c>
@@ -1425,7 +1386,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>44270</v>
       </c>
@@ -1442,7 +1403,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>44272</v>
       </c>
@@ -1459,7 +1420,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>44273</v>
       </c>
@@ -1476,7 +1437,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>44275</v>
       </c>
@@ -1493,7 +1454,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>44278</v>
       </c>
@@ -1510,7 +1471,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>44280</v>
       </c>
@@ -1527,7 +1488,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>44281</v>
       </c>
@@ -1544,7 +1505,7 @@
         <v>360000</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>44285</v>
       </c>
@@ -1561,7 +1522,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>44289</v>
       </c>
@@ -1578,7 +1539,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>44293</v>
       </c>
@@ -1595,7 +1556,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>44296</v>
       </c>
@@ -1612,7 +1573,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>44300</v>
       </c>
@@ -1629,7 +1590,7 @@
         <v>450000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>44304</v>
       </c>
@@ -1646,7 +1607,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>44308</v>
       </c>
@@ -1663,7 +1624,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>44311</v>
       </c>
